--- a/tame_output/ON/bt/strategyON_20231227.xlsx
+++ b/tame_output/ON/bt/strategyON_20231227.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.1%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>493.9%</t>
+          <t>487.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-163.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-132.9%</t>
+          <t>-133.0%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,32 +1283,32 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-704.2%</t>
+          <t>-501.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-18.6%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-3.827050467404899</v>
+        <v>-3.902349754011289</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.562163193113514</v>
+        <v>1.532043478470958</v>
       </c>
       <c r="F1788" t="n">
-        <v>-0.005241792804506484</v>
+        <v>-0.01323052787654866</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.090194728706518</v>
+        <v>3.085401487663293</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-3.837552656964245</v>
+        <v>-3.912851943570635</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.535726893080149</v>
+        <v>1.505607178437593</v>
       </c>
       <c r="F1789" t="n">
-        <v>-0.0157439823638531</v>
+        <v>-0.02373271743589528</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.061657990761284</v>
+        <v>3.056864749718058</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-3.839385919643362</v>
+        <v>-3.914685206249751</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.535694427854624</v>
+        <v>1.505574713212068</v>
       </c>
       <c r="F1790" t="n">
-        <v>-0.0157439823638531</v>
+        <v>-0.02373271743589528</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.062358830607405</v>
+        <v>3.05756558956418</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-3.844395034704946</v>
+        <v>-3.919694321311336</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.53420786165885</v>
+        <v>1.504088147016294</v>
       </c>
       <c r="F1791" t="n">
-        <v>-0.01673855992238782</v>
+        <v>-0.02472729499442999</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.062279163901144</v>
+        <v>3.057485922857918</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-3.84810059134176</v>
+        <v>-3.92339987794815</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.531953364244489</v>
+        <v>1.501833649601933</v>
       </c>
       <c r="F1792" t="n">
-        <v>-0.01860823518002275</v>
+        <v>-0.02659697025206492</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.060385083986928</v>
+        <v>3.055591842943703</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-3.846868265984395</v>
+        <v>-3.922167552590785</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.532866146449755</v>
+        <v>1.502746431807199</v>
       </c>
       <c r="F1793" t="n">
-        <v>-0.01797785880798519</v>
+        <v>-0.02596659388002737</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.06118316187247</v>
+        <v>3.056389920829245</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-3.836540268968542</v>
+        <v>-3.911839555574932</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.541127253420309</v>
+        <v>1.511007538777753</v>
       </c>
       <c r="F1794" t="n">
-        <v>-0.007649861792133006</v>
+        <v>-0.01563859686417518</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.071509868246195</v>
+        <v>3.06671662720297</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-3.836423933820987</v>
+        <v>-3.911723220427377</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.547694447681168</v>
+        <v>1.517574733038612</v>
       </c>
       <c r="F1795" t="n">
-        <v>-0.007533526644577293</v>
+        <v>-0.01552226171661947</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.078100329536565</v>
+        <v>3.073307088493339</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-3.838269343397854</v>
+        <v>-3.913568630004244</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.543930254295809</v>
+        <v>1.513810539653254</v>
       </c>
       <c r="F1796" t="n">
-        <v>-0.007533526644577293</v>
+        <v>-0.01552226171661947</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.075074299981953</v>
+        <v>3.070281058938728</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-3.836770910872755</v>
+        <v>-3.912070197479145</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.544467915166982</v>
+        <v>1.514348200524426</v>
       </c>
       <c r="F1797" t="n">
-        <v>-0.00603509411947839</v>
+        <v>-0.01402382919152056</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.075911647358146</v>
+        <v>3.071118406314921</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-3.844835163065489</v>
+        <v>-3.920134449671879</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.542520192233201</v>
+        <v>1.512400477590645</v>
       </c>
       <c r="F1798" t="n">
-        <v>-0.01409934631221221</v>
+        <v>-0.02208808138425439</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.072351073985817</v>
+        <v>3.067557832942592</v>
       </c>
     </row>
     <row r="1799">
@@ -42887,22 +42887,22 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-3.846165130526701</v>
+        <v>-3.921464417133091</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.541988205248716</v>
+        <v>1.51186849060616</v>
       </c>
       <c r="F1799" t="n">
-        <v>-0.01409934631221221</v>
+        <v>-0.02208808138425439</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.072351073985817</v>
+        <v>3.067557832942592</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.61830044779319</v>
+        <v>-3.69359973439958</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.635350551449282</v>
+        <v>1.605230836806726</v>
       </c>
       <c r="F1800" t="n">
-        <v>-0.01409934631221221</v>
+        <v>-0.02208808138425439</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.074567547092979</v>
+        <v>3.069774306049754</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-3.370198883925973</v>
+        <v>-3.445498170532363</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.742125773341261</v>
+        <v>1.712006058698705</v>
       </c>
       <c r="F1801" t="n">
-        <v>-0.01409934631221221</v>
+        <v>-0.02208808138425439</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.082102143438072</v>
+        <v>3.077308902394846</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-3.073360484532643</v>
+        <v>-3.148659771139033</v>
       </c>
       <c r="E1802" t="n">
-        <v>1.862284144072051</v>
+        <v>1.832164429429495</v>
       </c>
       <c r="F1802" t="n">
-        <v>0.1007551421689155</v>
+        <v>0.09276640709687328</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.152437847500206</v>
+        <v>3.14764460645698</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-2.769720927707206</v>
+        <v>-2.845020214313597</v>
       </c>
       <c r="E1803" t="n">
-        <v>1.985417041267912</v>
+        <v>1.955297326625355</v>
       </c>
       <c r="F1803" t="n">
-        <v>0.1007551421689155</v>
+        <v>0.09276640709687328</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.154114921965892</v>
+        <v>3.149321680922667</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-2.480700321266498</v>
+        <v>-2.555999607872888</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.096964705293653</v>
+        <v>2.066844990651096</v>
       </c>
       <c r="F1804" t="n">
-        <v>0.1007551421689155</v>
+        <v>0.09276640709687328</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.150054343415349</v>
+        <v>3.145261102372124</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-2.1959803940026</v>
+        <v>-2.271279680608991</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.216072815543229</v>
+        <v>2.185953100900673</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.3854750694328126</v>
+        <v>0.3774863343607704</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.326106439117706</v>
+        <v>3.32131319807448</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-1.91221872451106</v>
+        <v>-1.98751801111745</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.334889646513652</v>
+        <v>2.304769931871096</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.3854750694328126</v>
+        <v>0.3774863343607704</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.331418602291512</v>
+        <v>3.326625361248287</v>
       </c>
     </row>
     <row r="1807">
@@ -43077,16 +43077,16 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.650570330118419</v>
+        <v>-1.72586961672481</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.432791591717342</v>
+        <v>2.402671877074786</v>
       </c>
       <c r="F1807" t="n">
-        <v>0.6471234638254533</v>
+        <v>0.639134728753411</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.481650226373731</v>
+        <v>3.476856985330505</v>
       </c>
     </row>
     <row r="1808">
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-1.336403891979087</v>
+        <v>-1.411703178585477</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.555921841989188</v>
+        <v>2.525802127346632</v>
       </c>
       <c r="F1808" t="n">
-        <v>0.9612899019647857</v>
+        <v>0.9533011668927435</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.667613764273442</v>
+        <v>3.662820523230217</v>
       </c>
     </row>
     <row r="1809">
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-1.213892187873314</v>
+        <v>-1.289191474479705</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.623340907258236</v>
+        <v>2.59322119261568</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.083801606070558</v>
+        <v>1.075812870998516</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.759535170363645</v>
+        <v>3.75474192932042</v>
       </c>
     </row>
     <row r="1810">
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-1.052503653946586</v>
+        <v>-1.127802940552976</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.697712444884406</v>
+        <v>2.66759273024185</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.245190139997286</v>
+        <v>1.237201404925244</v>
       </c>
       <c r="G1810" t="n">
-        <v>3.866184414775161</v>
+        <v>3.861391173731935</v>
       </c>
     </row>
     <row r="1811">
@@ -43169,16 +43169,16 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-0.8727574627980798</v>
+        <v>-0.9480567494044702</v>
       </c>
       <c r="E1811" t="n">
-        <v>2.78313853339574</v>
+        <v>2.753018818753184</v>
       </c>
       <c r="F1811" t="n">
-        <v>1.245190139997286</v>
+        <v>1.237201404925244</v>
       </c>
       <c r="G1811" t="n">
-        <v>3.879712026827092</v>
+        <v>3.874918785783867</v>
       </c>
     </row>
     <row r="1812">
@@ -43192,16 +43192,16 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-0.7139565363268568</v>
+        <v>-0.7892558229332473</v>
       </c>
       <c r="E1812" t="n">
-        <v>2.853246284235495</v>
+        <v>2.823126569592939</v>
       </c>
       <c r="F1812" t="n">
-        <v>1.245190139997286</v>
+        <v>1.237201404925244</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.886299407078358</v>
+        <v>3.881506166035133</v>
       </c>
     </row>
     <row r="1813">
@@ -43215,16 +43215,16 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.62116807802148</v>
+        <v>-0.6964673646278704</v>
       </c>
       <c r="E1813" t="n">
-        <v>2.879272415992352</v>
+        <v>2.849152701349796</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.337978598302663</v>
+        <v>1.329989863230621</v>
       </c>
       <c r="G1813" t="n">
-        <v>3.93088323049629</v>
+        <v>3.926089989453065</v>
       </c>
     </row>
     <row r="1814">
@@ -43238,16 +43238,16 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>-0.5271475826506381</v>
+        <v>-0.6024468692570285</v>
       </c>
       <c r="E1814" t="n">
-        <v>2.912481111651413</v>
+        <v>2.882361397008857</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.347821038795647</v>
+        <v>1.339832303723605</v>
       </c>
       <c r="G1814" t="n">
-        <v>3.932389192302804</v>
+        <v>3.92759595125958</v>
       </c>
     </row>
     <row r="1815">
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>-0.437044614744115</v>
+        <v>-0.5123439013505054</v>
       </c>
       <c r="E1815" t="n">
-        <v>2.934502075320752</v>
+        <v>2.904382360678196</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.350879233083432</v>
+        <v>1.34289049801139</v>
       </c>
       <c r="G1815" t="n">
-        <v>3.920203885382206</v>
+        <v>3.915410644338981</v>
       </c>
     </row>
     <row r="1816">
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>-0.3929154440225399</v>
+        <v>-0.4682147306289303</v>
       </c>
       <c r="E1816" t="n">
-        <v>2.969603322364511</v>
+        <v>2.939483607721955</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.434898406070702</v>
+        <v>1.42690967099866</v>
       </c>
       <c r="G1816" t="n">
-        <v>3.988064967929697</v>
+        <v>3.983271726886472</v>
       </c>
     </row>
     <row r="1817">
@@ -43307,16 +43307,16 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>-0.3831453998448451</v>
+        <v>-0.4584446864512355</v>
       </c>
       <c r="E1817" t="n">
-        <v>2.972539390419666</v>
+        <v>2.94241967577711</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.514257297125769</v>
+        <v>1.506268562053727</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.034708352946813</v>
+        <v>4.029915111903589</v>
       </c>
     </row>
     <row r="1818">
@@ -43330,16 +43330,16 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>-0.3465070770768704</v>
+        <v>-0.4218063636832608</v>
       </c>
       <c r="E1818" t="n">
-        <v>2.976497440609699</v>
+        <v>2.946377725967142</v>
       </c>
       <c r="F1818" t="n">
-        <v>1.514257297125769</v>
+        <v>1.506268562053727</v>
       </c>
       <c r="G1818" t="n">
-        <v>4.024011074029656</v>
+        <v>4.019217832986431</v>
       </c>
     </row>
     <row r="1819">
@@ -43353,16 +43353,16 @@
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>-0.2978613986071371</v>
+        <v>-0.3731606852135275</v>
       </c>
       <c r="E1819" t="n">
-        <v>3.005872667459806</v>
+        <v>2.975752952817249</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.562902975595502</v>
+        <v>1.55491424052346</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.06311543657371</v>
+        <v>4.058322195530485</v>
       </c>
     </row>
     <row r="1820">
@@ -43376,16 +43376,16 @@
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>-0.2373814961877348</v>
+        <v>-0.3126807827941252</v>
       </c>
       <c r="E1820" t="n">
-        <v>3.036917606087114</v>
+        <v>3.006797891444558</v>
       </c>
       <c r="F1820" t="n">
-        <v>1.623382878014904</v>
+        <v>1.615394142942862</v>
       </c>
       <c r="G1820" t="n">
-        <v>4.106256355684899</v>
+        <v>4.101463114641674</v>
       </c>
     </row>
     <row r="1821">
@@ -43399,16 +43399,16 @@
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>-0.1548314286716178</v>
+        <v>-0.2301307152780082</v>
       </c>
       <c r="E1821" t="n">
-        <v>3.072161818709654</v>
+        <v>3.042042104067098</v>
       </c>
       <c r="F1821" t="n">
-        <v>1.623382878014904</v>
+        <v>1.615394142942862</v>
       </c>
       <c r="G1821" t="n">
-        <v>4.108480541300992</v>
+        <v>4.103687300257767</v>
       </c>
     </row>
     <row r="1822">
@@ -43422,16 +43422,16 @@
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>-0.07699534097640121</v>
+        <v>-0.1522946275827916</v>
       </c>
       <c r="E1822" t="n">
-        <v>3.089891278567524</v>
+        <v>3.059771563924968</v>
       </c>
       <c r="F1822" t="n">
-        <v>1.701964830671029</v>
+        <v>1.693976095598987</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.14222473767445</v>
+        <v>4.137431496631225</v>
       </c>
     </row>
     <row r="1823">
@@ -43445,16 +43445,16 @@
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>0.03988132463850408</v>
+        <v>-0.03541796196788632</v>
       </c>
       <c r="E1823" t="n">
-        <v>3.142307624339197</v>
+        <v>3.112187909696641</v>
       </c>
       <c r="F1823" t="n">
-        <v>1.784534172130654</v>
+        <v>1.776545437058612</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.197432022075936</v>
+        <v>4.192638781032711</v>
       </c>
     </row>
     <row r="1824">
@@ -43462,22 +43462,22 @@
         <v>45286</v>
       </c>
       <c r="B1824" t="n">
-        <v>3.164165174964625</v>
+        <v>3.166212125011356</v>
       </c>
       <c r="C1824" t="n">
         <v>3.130543841755795</v>
       </c>
       <c r="D1824" t="n">
-        <v>0.09474573389176094</v>
+        <v>0.09447028584918044</v>
       </c>
       <c r="E1824" t="n">
-        <v>3.168085710998753</v>
+        <v>3.167975531781721</v>
       </c>
       <c r="F1824" t="n">
-        <v>1.839398581383911</v>
+        <v>1.906433684875679</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.234182990586143</v>
+        <v>4.274404052681204</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231227.xlsx
+++ b/tame_output/ON/bt/strategyON_20231227.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -43468,16 +43468,16 @@
         <v>3.130543841755795</v>
       </c>
       <c r="D1824" t="n">
-        <v>0.09447028584918044</v>
+        <v>0.09455247940725736</v>
       </c>
       <c r="E1824" t="n">
-        <v>3.167975531781721</v>
+        <v>3.168008409204951</v>
       </c>
       <c r="F1824" t="n">
-        <v>1.906433684875679</v>
+        <v>1.906515878433755</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.274404052681204</v>
+        <v>4.27445336881605</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231227.xlsx
+++ b/tame_output/ON/bt/strategyON_20231227.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>487.2%</t>
+          <t>482.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-133.0%</t>
+          <t>-139.5%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-28.2%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-25.2%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728034</v>
+        <v>3.146730118728033</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702058</v>
+        <v>3.120735995702057</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -43468,16 +43468,16 @@
         <v>3.130543841755795</v>
       </c>
       <c r="D1824" t="n">
-        <v>0.09455247940725736</v>
+        <v>0.02913700638883382</v>
       </c>
       <c r="E1824" t="n">
-        <v>3.168008409204951</v>
+        <v>3.141842219997582</v>
       </c>
       <c r="F1824" t="n">
-        <v>1.906515878433755</v>
+        <v>1.841100405415332</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.27445336881605</v>
+        <v>4.235204085004995</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231227.xlsx
+++ b/tame_output/ON/bt/strategyON_20231227.xlsx
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728033</v>
+        <v>3.146730118728034</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702057</v>
+        <v>3.120735995702058</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
